--- a/branches/chore/reconcile-main-into-dev/StructureDefinition-example-patient.xlsx
+++ b/branches/chore/reconcile-main-into-dev/StructureDefinition-example-patient.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T07:52:27+00:00</t>
+    <t>2026-08-06T07:57:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
